--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -507,40 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17924</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15220</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,7 +817,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -826,31 +826,31 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,7 +879,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -888,31 +888,31 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -950,31 +950,31 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29778</v>
+        <v>33150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1003,40 +1003,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>29778</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="J10" t="n">

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,412 +507,412 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>551</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>551</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>551</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>551</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
           <t xml:space="preserve">stade raymond kopa
   angers </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E7" t="n">
         <v>18752</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>SAlF91iL</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>angers</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>lens</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>55</v>
-      </c>
-      <c r="K2" t="n">
-        <v>551</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>ripawyyS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>45522.5</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>55</v>
-      </c>
-      <c r="K3" t="n">
-        <v>551</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0js8u60b</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>551</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SOLVXEbk</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>551</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fHYrsJy3</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>551</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M5VGwpVA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la mosson
   montpellier </t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>20484</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>montpellier</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>55</v>
-      </c>
-      <c r="K7" t="n">
-        <v>551</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>lille</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -950,113 +950,671 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>551</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
           <t xml:space="preserve">roazhon park
   rennes </t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>29778</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>rennes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2akflumR</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>lyon</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>551</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ehlLyFq</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>MLmY2yB1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>toulouse</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K10" t="n">
-        <v>551</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="J16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>551</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>551</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>551</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>551</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,564 +1057,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>551</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>551</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>551</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>551</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>551</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>551</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>551</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>551</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,502 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>551</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>551</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>551</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>38223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -700,6 +700,698 @@
         </is>
       </c>
       <c r="O4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>551</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>551</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>551</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38223</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
+        <v>45535.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35322</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36178</v>
+        <v>20484</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>33150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67394</v>
+        <v>18523</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,40 +817,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59186</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -904,40 +879,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>25178</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -966,40 +941,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20484</v>
+        <v>21029</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1028,40 +1003,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>50186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1082,316 +1057,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>551</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>551</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>551</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>551</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,40 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>15220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.58333333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20484</v>
+        <v>33150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45536.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25178</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21029</v>
+        <v>50186</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -995,68 +1035,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K10" t="n">
-        <v>551</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18523</v>
+        <v>21029</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18752</v>
+        <v>50186</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -834,207 +834,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>55</v>
-      </c>
-      <c r="K7" t="n">
-        <v>551</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>55</v>
-      </c>
-      <c r="K8" t="n">
-        <v>551</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>551</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
+        <v>45548.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>42000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,35 +569,30 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
+        <v>45549.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>67394</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,45 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
+        <v>45549.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25178</v>
+        <v>17924</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>48229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -834,6 +809,254 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>551</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>551</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,564 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>551</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>551</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>551</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>551</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,333 +507,1154 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45555.65625</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>551</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>551</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>551</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>551</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>551</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>551</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>rennes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>montpellier</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>55</v>
-      </c>
-      <c r="K2" t="n">
-        <v>551</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>551</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>551</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la beaujoire
   nantes </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E18" t="n">
         <v>35322</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>nantes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>55</v>
-      </c>
-      <c r="K3" t="n">
-        <v>551</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>551</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
   strasbourg </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E19" t="n">
         <v>26109</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>strasbourg</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>551</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>551</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>551</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>551</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.65625</v>
+        <v>45556.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36178</v>
+        <v>50186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,40 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.5</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -636,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.58333333334</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29778</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -703,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.66666666666</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -770,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45557.41666666666</v>
+        <v>45557.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -837,7 +842,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -845,37 +850,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>15220</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -904,7 +909,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -912,37 +917,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,45 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.5</v>
+        <v>45557.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20484</v>
+        <v>59186</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1030,631 +1035,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K10" t="n">
-        <v>551</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45562.58333333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>551</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45562.66666666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>551</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.58333333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>551</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>551</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>551</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>551</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>551</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>551</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,333 +507,1114 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>551</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>551</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>551</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>551</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>551</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>551</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">roazhon park
   rennes </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E14" t="n">
         <v>29778</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>rennes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>551</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>montpellier</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>55</v>
-      </c>
-      <c r="K2" t="n">
-        <v>551</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>55</v>
-      </c>
-      <c r="K3" t="n">
-        <v>551</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="J17" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>551</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
   strasbourg </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E18" t="n">
         <v>26109</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>strasbourg</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>551</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>551</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>lens</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>551</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="J18" t="n">
+        <v>55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>551</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>551</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45562.58333333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de l abbe deschamps
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45562.66666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">parc des princes
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45563.5</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">stade bollaert delelis
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45563.58333333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">stade oceane
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45563.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">stade louis ii
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45564.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">stadium municipal
@@ -885,7 +915,12 @@
       <c r="B8" s="2" t="n">
         <v>45564.5</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stade raymond kopa
@@ -947,7 +982,12 @@
       <c r="B9" s="2" t="n">
         <v>45564.5</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la beaujoire
@@ -1009,7 +1049,12 @@
       <c r="B10" s="2" t="n">
         <v>45564.65625</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
@@ -1057,564 +1102,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>551</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.58333333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>551</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>551</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>551</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>551</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>551</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>551</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>551</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.58333333334</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17924</v>
+        <v>33150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48229</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38223</v>
+        <v>35322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.58333333334</v>
+        <v>45564.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -767,341 +767,6 @@
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>551</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>55</v>
-      </c>
-      <c r="K7" t="n">
-        <v>551</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>55</v>
-      </c>
-      <c r="K8" t="n">
-        <v>551</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kherradji a 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>551</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K10" t="n">
-        <v>551</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33150</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>42000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35322</v>
+        <v>50186</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,65 +708,462 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>551</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>551</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
   strasbourg </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>26109</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>strasbourg</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>55</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K9" t="n">
         <v>551</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M9" t="n">
         <v>20242025</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.5</v>
+        <v>45571.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42000</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.58333333334</v>
+        <v>45571.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50186</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45571.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29778</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +842,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
+        <v>45583.65625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -909,45 +904,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
+        <v>45584.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>15220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -976,35 +966,30 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
+        <v>45584.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26109</v>
+        <v>42000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1043,45 +1028,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
-        </is>
-      </c>
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36178</v>
+        <v>48229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1110,40 +1090,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18523</v>
+        <v>25178</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1164,6 +1144,254 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,333 +507,1154 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>551</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>551</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>551</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>551</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>551</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>551</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>551</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>551</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>551</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>551</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>551</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">stade oceane
   le havre </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E18" t="n">
         <v>25178</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>CIEe04GT</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>le havre</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>55</v>
-      </c>
-      <c r="K2" t="n">
-        <v>551</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>55</v>
-      </c>
-      <c r="K3" t="n">
-        <v>551</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>551</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la beaujoire
   nantes </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E19" t="n">
         <v>35322</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>nantes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>551</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>551</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>SblU3Hee</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>marseille</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>551</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="J19" t="n">
+        <v>55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>551</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45592.54166666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la mosson
@@ -1097,564 +1102,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>551</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.54166666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>551</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>551</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>551</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45599.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>551</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>551</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>551</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>551</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,564 +1102,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>551</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.54166666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>551</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>551</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>551</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>551</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>551</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>551</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>551</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>26109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.54166666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48229</v>
+        <v>38223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15220</v>
+        <v>18752</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,35 +842,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -909,45 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17924</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -976,45 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1043,45 +1043,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35322</v>
+        <v>59186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="J10" t="n">

--- a/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/france/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,6 +1102,254 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>551</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45618.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>551</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>551</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
